--- a/data/kz/14_competitors.xlsx
+++ b/data/kz/14_competitors.xlsx
@@ -527,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1760,7 +1761,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1811,7 +1812,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1862,7 +1863,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1909,7 +1910,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2247,6 +2248,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>

--- a/data/kz/14_competitors.xlsx
+++ b/data/kz/14_competitors.xlsx
@@ -527,7 +527,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -598,7 +597,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -649,7 +648,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -700,7 +699,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -751,7 +750,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -798,7 +797,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -845,7 +844,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -896,7 +895,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -943,7 +942,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -990,7 +989,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1037,7 +1036,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1084,7 +1083,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1135,7 +1134,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1182,7 +1181,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1229,7 +1228,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1276,7 +1275,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1323,7 +1322,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1374,7 +1373,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1421,7 +1420,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1472,7 +1471,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1519,7 +1518,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1570,7 +1569,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1621,7 +1620,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1672,7 +1671,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1719,7 +1718,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1766,7 +1765,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1817,7 +1816,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1868,7 +1867,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1915,7 +1914,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1962,7 +1961,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2013,7 +2012,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2060,7 +2059,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -2111,7 +2110,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -2158,7 +2157,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -2248,7 +2247,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
